--- a/data/archive/2026-09-28.xlsx
+++ b/data/archive/2026-09-28.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:37 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, Airports</t>
+          <t>Staff AI Engineer</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8806570002</t>
+          <t>5425364008</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
+          <t>https://job-boards.greenhouse.io/factored/jobs/5425364008</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,22 +754,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer</t>
+          <t>Backend Software Engineer, Airports</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5425364008</t>
+          <t>8806570002</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/factored/jobs/5425364008</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, Android (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8142961</t>
+          <t>6143238004</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8142961?gh_jid=8142961&amp;t=gh_src%3D</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:37 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1446,12 +1446,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, Backend (Summer 2027)</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1461,32 +1461,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Bellevue, WA; Menlo Park, CA; New York, NY</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8123225</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8123225?gh_jid=8123225&amp;t=gh_src%3D</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1533,57 +1533,53 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, iOS (Summer 2027)</t>
+          <t>Cybersecurity Engineer, Junior</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8142959</t>
+          <t>R0250290</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8142959?gh_jid=8142959&amp;t=gh_src%3D</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1598,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:42 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1620,27 +1616,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, Web (Summer 2027)</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>Rome, NY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1650,27 +1646,23 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8142963</t>
+          <t>R0248386</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8142963?gh_jid=8142963&amp;t=gh_src%3D</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1685,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:42 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1712,17 +1704,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1732,18 +1724,18 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>R0250290</t>
+          <t>R0248029</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1753,7 +1745,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1768,7 +1760,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:14 UTC</t>
+          <t>2026-09-28 16:42 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1782,353 +1774,13 @@
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Figma</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA • New York, NY</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6143238004</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:11 UTC</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>4736426005</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:11 UTC</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Rome, NY</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>R0248386</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:14 UTC</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>McLean, VA</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>R0248029</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:14 UTC</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q19"/>
+  <autoFilter ref="A1:Q15"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2152,10 +1804,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/archive/2026-09-28.xlsx
+++ b/data/archive/2026-09-28.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:37 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer</t>
+          <t>Backend Software Engineer, Airports</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>5425364008</t>
+          <t>8806570002</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/factored/jobs/5425364008</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, Airports</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8806570002</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Duolingo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>New York, NY; Pittsburgh, PA; Seattle, WA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -866,22 +866,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8180955</t>
+          <t>8805925002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
+          <t>https://careers.duolingo.com/jobs/8805925002?gh_jid=8805925002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Duolingo</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Intern - Spring 2027</t>
+          <t>Software Engineer, Thrive Intern</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6199367004</t>
+          <t>8806114002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
+          <t>https://careers.duolingo.com/jobs/8806114002?gh_jid=8806114002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Duolingo</t>
+          <t>Asana</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Senior Staff Software Engineer, Developer Productivity</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>New York, NY; Pittsburgh, PA; Seattle, WA</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8805925002</t>
+          <t>8212172</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://careers.duolingo.com/jobs/8805925002?gh_jid=8805925002</t>
+          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1102,12 +1102,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Duolingo</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Thrive Intern</t>
+          <t>Embedded Software Engineer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8806114002</t>
+          <t>8180955</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://careers.duolingo.com/jobs/8806114002?gh_jid=8806114002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Software Engineer, Developer Productivity</t>
+          <t>Software Engineering Intern - Spring 2027</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8212172</t>
+          <t>6199367004</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1359,57 +1359,53 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Cybersecurity Engineer, Junior</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>6143238004</t>
+          <t>R0250290</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:37 UTC</t>
+          <t>2026-09-28 19:01 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1446,22 +1442,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Rome, NY</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1471,32 +1467,28 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>R0248386</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1511,7 +1503,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 19:01 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1538,17 +1530,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1558,18 +1550,18 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>R0250290</t>
+          <t>R0248029</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1579,7 +1571,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1594,7 +1586,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:42 UTC</t>
+          <t>2026-09-28 19:01 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1608,179 +1600,13 @@
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Rome, NY</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>R0248386</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 16:42 UTC</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>McLean, VA</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>R0248029</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28 16:42 UTC</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q15"/>
+  <autoFilter ref="A1:Q13"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1802,8 +1628,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
